--- a/InputData/dist-heat/BFoHfC/BAU Fraction of Heat from CHP.xlsx
+++ b/InputData/dist-heat/BFoHfC/BAU Fraction of Heat from CHP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26216"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f0dd5cd5bd3d87a/Documents/IESR/Data Statistik/EPS Data/NEW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/dist-heat/BFoHfC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_2F28C21CC6E525A121EF322E9FCCA6117B0B0B41" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C0B0A0-DB19-4220-9494-1F3ABA5043D0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10275E0F-ED09-C341-8786-B6CBAFE5796D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -245,9 +245,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -285,9 +285,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -320,26 +320,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -372,26 +355,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -566,17 +532,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="47.73046875" customWidth="1"/>
+    <col min="2" max="2" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -584,57 +550,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -648,15 +614,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.59765625" customWidth="1"/>
-    <col min="2" max="2" width="21.59765625" customWidth="1"/>
-    <col min="3" max="3" width="32.1328125" customWidth="1"/>
-    <col min="4" max="4" width="22.59765625" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -670,7 +636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -684,7 +650,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -698,28 +664,28 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f>((C2/B2)*D2+(C3/B3)*D3)/SUM(D2:D3)</f>
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -734,14 +700,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:BE11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.265625" customWidth="1"/>
-    <col min="2" max="2" width="9.3984375" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:57" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
@@ -853,8 +819,68 @@
       <c r="AK1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -966,8 +992,68 @@
       <c r="AK2" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1079,8 +1165,68 @@
       <c r="AK3" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1192,8 +1338,68 @@
       <c r="AK4" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1305,8 +1511,68 @@
       <c r="AK5" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1418,8 +1684,68 @@
       <c r="AK6" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1531,8 +1857,68 @@
       <c r="AK7" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1644,8 +2030,68 @@
       <c r="AK8" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1757,8 +2203,68 @@
       <c r="AK9" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1870,8 +2376,68 @@
       <c r="AK10" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="AL10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1981,6 +2547,66 @@
         <v>0</v>
       </c>
       <c r="AK11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="8">
         <v>0</v>
       </c>
     </row>
